--- a/AAII_Financials/Yearly/FLD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLD_YR_FIN.xlsx
@@ -895,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>10500</v>
+        <v>10600</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -928,7 +928,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -973,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>60300</v>
+        <v>60200</v>
       </c>
       <c r="E17" s="3">
         <v>24300</v>
@@ -1006,7 +1006,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-28500</v>
+        <v>-28400</v>
       </c>
       <c r="E18" s="3">
         <v>-600</v>
